--- a/AC_2014/3-Karimnagar_7_030.xlsx
+++ b/AC_2014/3-Karimnagar_7_030.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -106,11 +111,33 @@
         <color rgb="00D3D3D3"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,6 +172,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -10395,10 +10431,10 @@
         <v>0</v>
       </c>
       <c r="S144" s="6" t="n">
-        <v>707</v>
+        <v>0</v>
       </c>
       <c r="T144" s="6" t="n">
-        <v>1149</v>
+        <v>442</v>
       </c>
       <c r="U144" s="6" t="n">
         <v>0</v>
@@ -17973,246 +18009,247 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="7" t="inlineStr">
+      <c r="A253" s="18" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B253" s="8" t="inlineStr"/>
-      <c r="C253" s="9">
+      <c r="B253" s="11" t="inlineStr"/>
+      <c r="C253" s="19">
         <f>SUM(C6:C252)</f>
         <v/>
       </c>
-      <c r="D253" s="9">
+      <c r="D253" s="19">
         <f>SUM(D6:D252)</f>
         <v/>
       </c>
-      <c r="E253" s="9">
+      <c r="E253" s="19">
         <f>SUM(E6:E252)</f>
         <v/>
       </c>
-      <c r="F253" s="9">
+      <c r="F253" s="19">
         <f>SUM(F6:F252)</f>
         <v/>
       </c>
-      <c r="G253" s="9">
+      <c r="G253" s="19">
         <f>SUM(G6:G252)</f>
         <v/>
       </c>
-      <c r="H253" s="9">
+      <c r="H253" s="19">
         <f>SUM(H6:H252)</f>
         <v/>
       </c>
-      <c r="I253" s="9">
+      <c r="I253" s="19">
         <f>SUM(I6:I252)</f>
         <v/>
       </c>
-      <c r="J253" s="9">
+      <c r="J253" s="19">
         <f>SUM(J6:J252)</f>
         <v/>
       </c>
-      <c r="K253" s="9">
+      <c r="K253" s="19">
         <f>SUM(K6:K252)</f>
         <v/>
       </c>
-      <c r="L253" s="9">
+      <c r="L253" s="19">
         <f>SUM(L6:L252)</f>
         <v/>
       </c>
-      <c r="M253" s="9">
+      <c r="M253" s="19">
         <f>SUM(M6:M252)</f>
         <v/>
       </c>
-      <c r="N253" s="9">
+      <c r="N253" s="19">
         <f>SUM(N6:N252)</f>
         <v/>
       </c>
-      <c r="O253" s="9">
+      <c r="O253" s="19">
         <f>SUM(O6:O252)</f>
         <v/>
       </c>
-      <c r="P253" s="9">
+      <c r="P253" s="19">
         <f>SUM(P6:P252)</f>
         <v/>
       </c>
-      <c r="Q253" s="9">
+      <c r="Q253" s="19">
         <f>SUM(Q6:Q252)</f>
         <v/>
       </c>
-      <c r="R253" s="9">
+      <c r="R253" s="19">
         <f>SUM(R6:R252)</f>
         <v/>
       </c>
-      <c r="S253" s="9">
+      <c r="S253" s="19">
         <f>SUM(S6:S252)</f>
         <v/>
       </c>
-      <c r="T253" s="9">
+      <c r="T253" s="19">
         <f>SUM(T6:T252)</f>
         <v/>
       </c>
-      <c r="U253" s="9">
+      <c r="U253" s="19">
         <f>SUM(U6:U252)</f>
         <v/>
       </c>
-      <c r="V253" s="9">
+      <c r="V253" s="19">
         <f>SUM(V6:V252)</f>
         <v/>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="10" t="inlineStr">
+      <c r="A254" s="18" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B254" s="11" t="inlineStr"/>
-      <c r="C254" s="12" t="n">
+      <c r="C254" s="19" t="n">
         <v>194</v>
       </c>
-      <c r="D254" s="12" t="n">
+      <c r="D254" s="19" t="n">
         <v>57</v>
       </c>
-      <c r="E254" s="12" t="n">
+      <c r="E254" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="F254" s="12" t="n">
+      <c r="F254" s="19" t="n">
         <v>201</v>
       </c>
-      <c r="G254" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H254" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I254" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J254" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K254" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L254" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M254" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N254" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O254" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P254" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q254" s="12" t="n">
+      <c r="G254" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I254" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L254" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M254" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N254" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O254" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q254" s="19" t="n">
         <v>459</v>
       </c>
-      <c r="R254" s="12" t="n">
+      <c r="R254" s="19" t="n">
         <v>60</v>
       </c>
-      <c r="S254" s="12" t="n">
+      <c r="S254" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="T254" s="12" t="n">
+      <c r="T254" s="19" t="n">
         <v>522</v>
       </c>
-      <c r="U254" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V254" s="13" t="n">
+      <c r="U254" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V254" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="14" t="inlineStr">
+      <c r="A255" s="18" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B255" s="15" t="inlineStr"/>
-      <c r="C255" s="16">
+      <c r="B255" s="11" t="inlineStr"/>
+      <c r="C255" s="20">
         <f>C253+C254</f>
         <v/>
       </c>
-      <c r="D255" s="16">
+      <c r="D255" s="20">
         <f>D253+D254</f>
         <v/>
       </c>
-      <c r="E255" s="16">
+      <c r="E255" s="20">
         <f>E253+E254</f>
         <v/>
       </c>
-      <c r="F255" s="16">
+      <c r="F255" s="20">
         <f>F253+F254</f>
         <v/>
       </c>
-      <c r="G255" s="16">
+      <c r="G255" s="20">
         <f>G253+G254</f>
         <v/>
       </c>
-      <c r="H255" s="16">
+      <c r="H255" s="20">
         <f>H253+H254</f>
         <v/>
       </c>
-      <c r="I255" s="16">
+      <c r="I255" s="20">
         <f>I253+I254</f>
         <v/>
       </c>
-      <c r="J255" s="16">
+      <c r="J255" s="20">
         <f>J253+J254</f>
         <v/>
       </c>
-      <c r="K255" s="16">
+      <c r="K255" s="20">
         <f>K253+K254</f>
         <v/>
       </c>
-      <c r="L255" s="16">
+      <c r="L255" s="20">
         <f>L253+L254</f>
         <v/>
       </c>
-      <c r="M255" s="16">
+      <c r="M255" s="20">
         <f>M253+M254</f>
         <v/>
       </c>
-      <c r="N255" s="16">
+      <c r="N255" s="20">
         <f>N253+N254</f>
         <v/>
       </c>
-      <c r="O255" s="16">
+      <c r="O255" s="20">
         <f>O253+O254</f>
         <v/>
       </c>
-      <c r="P255" s="16">
+      <c r="P255" s="20">
         <f>P253+P254</f>
         <v/>
       </c>
-      <c r="Q255" s="16">
+      <c r="Q255" s="20">
         <f>Q253+Q254</f>
         <v/>
       </c>
-      <c r="R255" s="16">
+      <c r="R255" s="20">
         <f>R253+R254</f>
         <v/>
       </c>
-      <c r="S255" s="16">
+      <c r="S255" s="20">
         <f>S253+S254</f>
         <v/>
       </c>
-      <c r="T255" s="16">
+      <c r="T255" s="20">
         <f>T253+T254</f>
         <v/>
       </c>
-      <c r="U255" s="16">
+      <c r="U255" s="20">
         <f>U253+U254</f>
         <v/>
       </c>
-      <c r="V255" s="17" t="n">
-        <v>0</v>
+      <c r="V255" s="20">
+        <f>V253+V254</f>
+        <v/>
       </c>
     </row>
   </sheetData>
